--- a/docs/sprint-11-citweb/pbi-7762/evidencias/CT-RAP-RETESTE-7975/Analitico-Producao-Int-07-2026.xlsx
+++ b/docs/sprint-11-citweb/pbi-7762/evidencias/CT-RAP-RETESTE-7975/Analitico-Producao-Int-07-2026.xlsx
@@ -26,7 +26,7 @@
     <t>CRITÉRIO DE SELEÇÃO: TUDO</t>
   </si>
   <si>
-    <t>Gerado em 04/08/2026 10:05</t>
+    <t>Gerado em 04/08/2026 10:36</t>
   </si>
   <si>
     <t>Ano/Mês Refer</t>

--- a/docs/sprint-11-citweb/pbi-7762/evidencias/CT-RAP-RETESTE-7975/Analitico-Producao-Int-07-2026.xlsx
+++ b/docs/sprint-11-citweb/pbi-7762/evidencias/CT-RAP-RETESTE-7975/Analitico-Producao-Int-07-2026.xlsx
@@ -26,7 +26,7 @@
     <t>CRITÉRIO DE SELEÇÃO: TUDO</t>
   </si>
   <si>
-    <t>Gerado em 04/08/2026 10:36</t>
+    <t>Gerado em 05/08/2026 10:39</t>
   </si>
   <si>
     <t>Ano/Mês Refer</t>
@@ -197,7 +197,7 @@
     <t>CITNET</t>
   </si>
   <si>
-    <t>MENSAL DET</t>
+    <t>AVERBÁVEL</t>
   </si>
   <si>
     <t xml:space="preserve">4TECH MAQUINAS E EQUIPAMENTOS LTDA                                                                  </t>
@@ -293,10 +293,10 @@
     <t>ANDREIA</t>
   </si>
   <si>
-    <t>6.029.924.709,24</t>
-  </si>
-  <si>
-    <t>21.501.024,17</t>
+    <t>6.035.534.194,27</t>
+  </si>
+  <si>
+    <t>21.521.024,17</t>
   </si>
   <si>
     <t>DIÁRIA</t>
